--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S1-01-01</t>
+          <t>S1-01-61</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5401</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dlalelu al</t>
+          <t>Naaa</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AIZU</t>
+          <t>RAZ</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G02B</t>
+          <t>G02H</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G02H</t>
+          <t>G02F</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Naaa</t>
+          <t>Mara</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RAZ</t>
+          <t>PAZ</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mara</t>
+          <t>MARA</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62598.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
